--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>133275252</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,11 +817,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -1006,7 +1002,7 @@
         <v>134156084</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,11 +1030,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>133275252</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>134156084</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>133275252</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>134156084</v>
       </c>
       <c r="B5" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
